--- a/servers/maze_main_server/conf.d/data/maze_action_count_v8【行为次数】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_action_count_v8【行为次数】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBC7D52-7AAD-4C49-B66D-36A7628835EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B93B063-284F-452F-8B99-1889E2597DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/servers/maze_main_server/conf.d/data/maze_action_count_v8【行为次数】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_action_count_v8【行为次数】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF1E0DF-1F14-4E6E-8BA1-6C6081FF3162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBC7D52-7AAD-4C49-B66D-36A7628835EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -646,7 +646,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="3">
-        <v>100000</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>17</v>

--- a/servers/maze_main_server/conf.d/data/maze_action_count_v8【行为次数】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_action_count_v8【行为次数】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B93B063-284F-452F-8B99-1889E2597DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBC7D52-7AAD-4C49-B66D-36A7628835EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/servers/maze_main_server/conf.d/data/maze_action_count_v8【行为次数】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_action_count_v8【行为次数】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBC7D52-7AAD-4C49-B66D-36A7628835EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CD2E41-80BF-41B0-B135-F9AFFE261D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_action_count_v8" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,7 +551,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.75" style="2" bestFit="1" customWidth="1"/>
@@ -561,7 +561,7 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -570,7 +570,7 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="1:5" s="1" customFormat="1">
+    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -587,7 +587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="1" customFormat="1">
+    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -604,7 +604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="1" customFormat="1">
+    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -621,7 +621,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -638,7 +638,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>101</v>
       </c>
@@ -646,7 +646,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="3">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>17</v>
@@ -655,7 +655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
         <v>102</v>
       </c>
